--- a/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
+++ b/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\samples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\可识别文件夹里面嵌套的表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
   <si>
     <t>table: Item</t>
   </si>
@@ -1203,10 +1203,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1322,6 +1322,94 @@
         <v>20</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="2">
+        <v>2006</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="2">
+        <v>2008</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="2">
+        <v>2011</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="2">
+        <v>2012</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
+++ b/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="22">
   <si>
     <t>table: Item</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>price</t>
+  </si>
+  <si>
+    <t>skill_id</t>
   </si>
   <si>
     <t>客户端服务器</t>
@@ -1203,14 +1206,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="37" customHeight="1" spans="1:4">
+    <row r="1" ht="37" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:4">
+    <row r="2" ht="15" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1238,7 +1241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:4">
+    <row r="3" ht="15" customHeight="1" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1251,8 +1254,11 @@
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:4">
+      <c r="E3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1265,36 +1271,42 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:4">
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
@@ -1302,13 +1314,16 @@
         <v>2003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:4">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -1316,99 +1331,114 @@
         <v>2004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="B9" s="2">
         <v>2005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="B10" s="2">
         <v>2006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="B11" s="2">
         <v>2007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
       <c r="B12" s="2">
         <v>2008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
       <c r="B13" s="2">
         <v>2009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
       <c r="B14" s="2">
         <v>2010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
       <c r="B15" s="2">
         <v>2011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="B16" s="2">
         <v>2012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="E16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
+++ b/UnityTableTool/Data/可识别文件夹里面嵌套的表格/道具表_1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\文档\codex\Game_Tools\UnityTableTool\Data\可识别文件夹里面嵌套的表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Game_Tools\UnityTableTool\Data\可识别文件夹里面嵌套的表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
@@ -1209,7 +1209,7 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="4" width="18.625" style="1" customWidth="1"/>
+    <col min="1" max="4" width="18.6272727272727" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1350,9 +1350,7 @@
       <c r="D9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="2">
-        <v>1043</v>
-      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="2">
@@ -1364,9 +1362,7 @@
       <c r="D10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="2">
-        <v>1044</v>
-      </c>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="2">
